--- a/case_studies/current_layout/technologies.xlsx
+++ b/case_studies/current_layout/technologies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\backbone_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\current_layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B7F995-16AD-4DF2-925D-4F55DD5167F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82AA6A8-DE5A-40F5-A7C3-C8D0A9DA358B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="3" r:id="rId1"/>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -1261,6 +1261,9 @@
         <v>0</v>
       </c>
       <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
         <v>0</v>
       </c>
     </row>
@@ -1340,6 +1343,9 @@
       <c r="Y3">
         <v>0</v>
       </c>
+      <c r="Z3">
+        <v>45</v>
+      </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1367,13 +1373,13 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J4">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1400,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -1416,6 +1422,9 @@
       </c>
       <c r="Y4">
         <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
@@ -1450,7 +1459,7 @@
         <v>79</v>
       </c>
       <c r="K5">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1493,6 +1502,9 @@
       </c>
       <c r="Y5">
         <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
@@ -1521,13 +1533,13 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1554,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -1569,6 +1581,9 @@
         <v>0</v>
       </c>
       <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
         <v>0</v>
       </c>
     </row>
@@ -1648,6 +1663,9 @@
       <c r="Y7">
         <v>0</v>
       </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1708,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -1723,6 +1741,9 @@
         <v>0</v>
       </c>
       <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>

--- a/case_studies/current_layout/technologies.xlsx
+++ b/case_studies/current_layout/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\current_layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82AA6A8-DE5A-40F5-A7C3-C8D0A9DA358B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F6D653-8C50-4C49-9B7B-31FC524023C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="38">
   <si>
     <t>cluster</t>
   </si>
@@ -137,6 +137,21 @@
   </si>
   <si>
     <t>CO2toEmissions</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_BE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_DE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_NL</t>
+  </si>
+  <si>
+    <t>H2_network_connection_in</t>
+  </si>
+  <si>
+    <t>H2_network_connection_out</t>
   </si>
 </sst>
 </file>
@@ -454,10 +469,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32646D9-68BB-474D-B725-BABE5F54D2FA}">
-  <dimension ref="A1:Z8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -536,8 +551,23 @@
       <c r="Z1" t="s">
         <v>32</v>
       </c>
+      <c r="AA1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -616,8 +646,23 @@
       <c r="Z2">
         <v>0</v>
       </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -696,8 +741,23 @@
       <c r="Z3">
         <v>0</v>
       </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -776,8 +836,23 @@
       <c r="Z4">
         <v>0</v>
       </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -856,8 +931,23 @@
       <c r="Z5">
         <v>0</v>
       </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -936,8 +1026,23 @@
       <c r="Z6">
         <v>0</v>
       </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1016,8 +1121,23 @@
       <c r="Z7">
         <v>0</v>
       </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1094,6 +1214,21 @@
         <v>0</v>
       </c>
       <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
         <v>0</v>
       </c>
     </row>
@@ -1105,9 +1240,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B7B1BB4-9645-4A08-BE86-AFBC7A2F79A5}">
   <dimension ref="A1:Z8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1187,7 +1322,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1267,7 +1402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1347,7 +1482,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1427,7 +1562,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1507,7 +1642,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1587,7 +1722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1667,7 +1802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1754,10 +1889,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:Z8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1836,8 +1971,23 @@
       <c r="Z1" t="s">
         <v>32</v>
       </c>
+      <c r="AA1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1916,8 +2066,23 @@
       <c r="Z2">
         <v>1</v>
       </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1996,8 +2161,23 @@
       <c r="Z3">
         <v>1</v>
       </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2076,8 +2256,23 @@
       <c r="Z4">
         <v>1</v>
       </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2156,8 +2351,23 @@
       <c r="Z5">
         <v>1</v>
       </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2236,8 +2446,23 @@
       <c r="Z6">
         <v>1</v>
       </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2316,8 +2541,23 @@
       <c r="Z7">
         <v>1</v>
       </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -2395,6 +2635,21 @@
       </c>
       <c r="Z8">
         <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
